--- a/Tables/aov_shoot_table_GlucoseQuantity.xlsx
+++ b/Tables/aov_shoot_table_GlucoseQuantity.xlsx
@@ -392,17 +392,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>0.289</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19.962</t>
+          <t>0.292</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>&lt; 0.001</t>
+          <t>0.747</t>
         </is>
       </c>
     </row>
@@ -417,17 +417,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>6.226</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.659</t>
+          <t>12.568</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>&lt; 0.001</t>
         </is>
       </c>
     </row>
@@ -442,17 +442,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.205</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>0.207</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.895</t>
+          <t>0.813</t>
         </is>
       </c>
     </row>
@@ -467,7 +467,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.129</t>
+          <t>166.455</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
